--- a/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:43:57+00:00</t>
+    <t>2026-09-02T12:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>DeviceUseStatement.reasonReference</t>
+  </si>
+  <si>
+    <t>FRObservationALDDocument / FRObservationWorkRelatedAccidentDocument / FRObservationPreventionDocument</t>
   </si>
   <si>
     <t>DeviceUseStatement.note</t>
@@ -700,7 +703,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -893,46 +896,22 @@
       <c r="D14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>71</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:54:48+00:00</t>
+    <t>2026-09-02T15:48:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:48:56+00:00</t>
+    <t>2026-09-03T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:02:14+00:00</t>
+    <t>2026-09-03T10:35:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
+++ b/fix-mapping-entete-duplicate-targets/ig/FRDeviceUseLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:35:28+00:00</t>
+    <t>2026-09-04T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
